--- a/datos.xlsx
+++ b/datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samke\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\OneDrive\Desktop\Repositorios\Hidro1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330D6458-A503-4F40-92C0-4C13D12776B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E986B5-498A-45FC-8808-D7296A1CA8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{4946304E-808B-4F57-9620-AE781020ABA9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{4946304E-808B-4F57-9620-AE781020ABA9}"/>
   </bookViews>
   <sheets>
     <sheet name="PropiedadesAgua" sheetId="2" r:id="rId1"/>
@@ -173,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -195,7 +195,6 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,13 +452,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3DD00A-F079-4DED-BBD0-593E59863DD3}">
   <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.3984375" customWidth="1"/>
-    <col min="5" max="5" width="23.8984375" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="5" max="5" width="23.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -473,7 +472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>0</v>
       </c>
@@ -487,7 +486,7 @@
         <v>1.781E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>5</v>
       </c>
@@ -501,7 +500,7 @@
         <v>1.518E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>10</v>
       </c>
@@ -516,7 +515,7 @@
       </c>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>15</v>
       </c>
@@ -530,7 +529,7 @@
         <v>1.139E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>20</v>
       </c>
@@ -544,7 +543,7 @@
         <v>1.1019999999999999E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>25</v>
       </c>
@@ -558,7 +557,7 @@
         <v>8.8999999999999995E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>30</v>
       </c>
@@ -572,7 +571,7 @@
         <v>7.0799999999999997E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>40</v>
       </c>
@@ -586,7 +585,7 @@
         <v>6.5300000000000004E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>50</v>
       </c>
@@ -601,7 +600,7 @@
       </c>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>60</v>
       </c>
@@ -615,7 +614,7 @@
         <v>4.66E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>70</v>
       </c>
@@ -629,7 +628,7 @@
         <v>4.0400000000000001E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>80</v>
       </c>
@@ -643,7 +642,7 @@
         <v>3.5399999999999999E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>90</v>
       </c>
@@ -658,7 +657,7 @@
       </c>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>100</v>
       </c>
@@ -672,17 +671,17 @@
         <v>2.8200000000000002E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B16" s="4"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="4"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
     </row>
   </sheetData>
@@ -694,13 +693,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831BE60F-005F-43D4-92C1-B89A902BA3E4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -723,7 +722,7 @@
         <v>2.377871479502114E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -735,7 +734,7 @@
         <v>4.1187065086725587E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -747,7 +746,7 @@
         <v>6.7886675651421843E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -759,7 +758,7 @@
         <v>2.2912137877454931E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -771,7 +770,7 @@
         <v>3.9690127603216589E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -783,7 +782,7 @@
         <v>6.0961003230656607E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -795,7 +794,7 @@
         <v>2.0611989400202629E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -807,7 +806,7 @@
         <v>3.3329156461934118E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -826,14 +825,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C561C54-6F92-4AE5-AE7C-79990FF069F8}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.09765625" customWidth="1"/>
-    <col min="2" max="2" width="26.19921875" customWidth="1"/>
+    <col min="1" max="1" width="39.125" customWidth="1"/>
+    <col min="2" max="2" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -841,7 +840,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -849,7 +848,7 @@
         <v>1.5E-6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -857,16 +856,13 @@
         <v>1.5E-6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
       <c r="B4">
-        <v>1.4999999999999999E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="11"/>
+        <v>1.5E-6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\OneDrive\Desktop\Repositorios\Hidro1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E986B5-498A-45FC-8808-D7296A1CA8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCF2D29-FD79-4083-B347-63D1B6A04151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{4946304E-808B-4F57-9620-AE781020ABA9}"/>
   </bookViews>
@@ -22,15 +22,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -105,11 +96,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.0000E+00"/>
     <numFmt numFmtId="166" formatCode="0.0000000000"/>
     <numFmt numFmtId="167" formatCode="0.0000000"/>
+    <numFmt numFmtId="168" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -173,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -195,6 +187,7 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,7 +837,7 @@
       <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="11">
         <v>1.5E-6</v>
       </c>
     </row>
@@ -852,15 +845,15 @@
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3">
-        <v>1.5E-6</v>
+      <c r="B3" s="11">
+        <v>1.4999999999999999E-4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="11">
         <v>1.5E-6</v>
       </c>
     </row>
